--- a/GD32F103C8T6核心板-BOM.xlsx
+++ b/GD32F103C8T6核心板-BOM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\PCB_projects\GD32F103C8T6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\PCB_Projects\GB32F103C8T6_PCB_Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5DD8410-5CE4-40BE-AEA5-966A48ECA260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C86FC2D6-C0B8-4DF2-8265-F1216E6DDFAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="16440" windowHeight="28320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM_C500624-GD32F103C8T6方案验证板 c" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="143">
   <si>
     <t>No.</t>
   </si>
@@ -61,9 +61,6 @@
     <t>20pF</t>
   </si>
   <si>
-    <t>C1,C2,C3,C4</t>
-  </si>
-  <si>
     <t>0603</t>
   </si>
   <si>
@@ -76,9 +73,6 @@
     <t>FH</t>
   </si>
   <si>
-    <t>C91702</t>
-  </si>
-  <si>
     <t>JHP硬件工作室</t>
   </si>
   <si>
@@ -91,36 +85,24 @@
     <t>1uF</t>
   </si>
   <si>
-    <t>C5,C7,C8,C10,C13,C15</t>
-  </si>
-  <si>
     <t>CL10A105KP8NNNC</t>
   </si>
   <si>
     <t>SAMSUNG</t>
   </si>
   <si>
-    <t>C26413</t>
-  </si>
-  <si>
     <t>3</t>
   </si>
   <si>
     <t>10nF</t>
   </si>
   <si>
-    <t>C6,C9,C11,C12,C14,C16</t>
-  </si>
-  <si>
     <t>CC0603KRX7R9BB103</t>
   </si>
   <si>
     <t>YAGEO</t>
   </si>
   <si>
-    <t>C100042</t>
-  </si>
-  <si>
     <t>100nF</t>
   </si>
   <si>
@@ -145,18 +127,12 @@
     <t>22uF</t>
   </si>
   <si>
-    <t>C19</t>
-  </si>
-  <si>
     <t>CL21A226MAQNNNE</t>
   </si>
   <si>
     <t>SAMSUNG(三星)</t>
   </si>
   <si>
-    <t>C45783</t>
-  </si>
-  <si>
     <t>7</t>
   </si>
   <si>
@@ -172,9 +148,6 @@
     <t>RUILON</t>
   </si>
   <si>
-    <t>C15997</t>
-  </si>
-  <si>
     <t>8</t>
   </si>
   <si>
@@ -205,9 +178,6 @@
     <t>BOOMELE</t>
   </si>
   <si>
-    <t>C50981</t>
-  </si>
-  <si>
     <t>10</t>
   </si>
   <si>
@@ -244,15 +214,9 @@
     <t>10K</t>
   </si>
   <si>
-    <t>R1,R2,R4</t>
-  </si>
-  <si>
     <t>RC0603JR-0710KL</t>
   </si>
   <si>
-    <t>C99198</t>
-  </si>
-  <si>
     <t>13</t>
   </si>
   <si>
@@ -265,9 +229,6 @@
     <t>RC0603JR-071ML</t>
   </si>
   <si>
-    <t>C107698</t>
-  </si>
-  <si>
     <t>14</t>
   </si>
   <si>
@@ -331,9 +292,6 @@
     <t>BRIGHT</t>
   </si>
   <si>
-    <t>C294564</t>
-  </si>
-  <si>
     <t>19</t>
   </si>
   <si>
@@ -349,9 +307,6 @@
     <t>GigaDevice</t>
   </si>
   <si>
-    <t>C77994</t>
-  </si>
-  <si>
     <t>20</t>
   </si>
   <si>
@@ -379,9 +334,6 @@
     <t>HRO</t>
   </si>
   <si>
-    <t>C91467</t>
-  </si>
-  <si>
     <t>22</t>
   </si>
   <si>
@@ -400,9 +352,6 @@
     <t>YXC</t>
   </si>
   <si>
-    <t>C21263</t>
-  </si>
-  <si>
     <t>23</t>
   </si>
   <si>
@@ -419,9 +368,6 @@
   </si>
   <si>
     <t>YXC(扬兴晶振)</t>
-  </si>
-  <si>
-    <t>C52082</t>
   </si>
   <si>
     <t>C84263</t>
@@ -488,6 +434,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -522,6 +469,180 @@
   </si>
   <si>
     <t>C492421</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C91467</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>C5,C7,C8,C10,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C13</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,C15</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C26413</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C19</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C45783</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>C6,C9,C11,C12,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C14</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,C16</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C100042</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C15997</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C50981</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C99198</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C294564</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>R1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>R2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,R4</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C21263</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C107698</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>C1,C2,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C3,C4</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C91702</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C52082</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C77994</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -694,7 +815,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="CAEACE"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -1009,15 +1130,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="20" style="1" customWidth="1"/>
-    <col min="4" max="4" width="37.375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="37.36328125" style="1" customWidth="1"/>
     <col min="5" max="10" width="20" style="1" customWidth="1"/>
     <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1049,745 +1170,745 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="D3" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="I3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="1" t="s">
+      <c r="B4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="D4" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A4" s="1" t="s">
+      <c r="I4" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="D5" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="H5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>29</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="I7" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="B8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="1" t="s">
+      <c r="E8" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="F8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H8" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" s="1" t="s">
+      <c r="I8" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="B9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="D9" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A8" s="1" t="s">
+      <c r="F9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="1" t="s">
+      <c r="I9" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="B10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H8" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="F10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="J8" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A9" s="1" t="s">
+      <c r="H10" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="1" t="s">
+      <c r="I10" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A10" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A11" s="1" t="s">
-        <v>62</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D13" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11" s="1" t="s">
+      <c r="H13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="H11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I11" s="1" t="s">
+      <c r="B14" s="3">
+        <v>1</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="J11" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" s="3" t="s">
+      <c r="E14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="H14" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="B15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="H12" s="3" t="s">
+      <c r="D15" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="I12" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A13" s="1" t="s">
+      <c r="H15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" s="1" t="s">
+      <c r="B16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D16" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13" s="1" t="s">
+      <c r="E16" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H13" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" s="1" t="s">
+      <c r="F16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="J13" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A14" s="1" t="s">
+      <c r="H16" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="1" t="s">
+      <c r="I16" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="J16" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G14" s="1" t="s">
+      <c r="B17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="H14" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I14" s="1" t="s">
+      <c r="D17" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="J14" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="3" t="s">
+      <c r="E17" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" s="3" t="s">
+      <c r="B18" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G15" s="3" t="s">
+      <c r="D18" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I15" s="4" t="s">
+      <c r="E18" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="I19" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A16" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="H16" s="1" t="s">
+      <c r="J19" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A17" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A18" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A19" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A20" s="1" t="s">
-        <v>104</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>109</v>
+        <v>94</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>142</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>119</v>
+        <v>103</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A23" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B23" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A24" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B24" s="1" t="s">
+      <c r="C23" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="C24" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/GD32F103C8T6核心板-BOM.xlsx
+++ b/GD32F103C8T6核心板-BOM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\PCB_Projects\GB32F103C8T6_PCB_Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9BDFE29-7A95-4766-AFE5-DA29AE788240}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D7155B7-8CFA-4752-AD42-18B9923227D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="11440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM_C500624-GD32F103C8T6方案验证板 c" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="144">
   <si>
     <t>No.</t>
   </si>
@@ -771,6 +771,10 @@
   </si>
   <si>
     <t>Header-Male-2.54_1x20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C15402</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1769,7 +1773,7 @@
         <v>75</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>76</v>
+        <v>143</v>
       </c>
       <c r="J16" s="1" t="s">
         <v>17</v>

--- a/GD32F103C8T6核心板-BOM.xlsx
+++ b/GD32F103C8T6核心板-BOM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\PCB_Projects\GB32F103C8T6_PCB_Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D7155B7-8CFA-4752-AD42-18B9923227D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00A80FC4-6202-4EA3-9FFD-4D07A1B6BD4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="11440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM_C500624-GD32F103C8T6方案验证板 c" sheetId="1" r:id="rId1"/>
@@ -857,74 +857,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1747,99 +1679,99 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+    <row r="16" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G16" s="1" t="s">
+      <c r="F16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="H16" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="I16" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="J16" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+      <c r="J16" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E17" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="F17" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G17" s="1" t="s">
+      <c r="F17" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="H17" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="I17" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="J17" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+      <c r="J17" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E18" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="F18" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G18" s="1" t="s">
+      <c r="F18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="H18" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="I18" s="1" t="s">
+      <c r="I18" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="J18" s="1" t="s">
+      <c r="J18" s="2" t="s">
         <v>17</v>
       </c>
     </row>
